--- a/artfynd/A 46152-2021 artfynd.xlsx
+++ b/artfynd/A 46152-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46152-2021 artfynd.xlsx
+++ b/artfynd/A 46152-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,117 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120288379</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>St Lappträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>862228</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7347558</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Töre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46152-2021 artfynd.xlsx
+++ b/artfynd/A 46152-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>120288379</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46152-2021 artfynd.xlsx
+++ b/artfynd/A 46152-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97909533</v>
+        <v>104154369</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>St Lappträsk, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862228.1429796738</v>
+        <v>862227</v>
       </c>
       <c r="R2" t="n">
-        <v>7347558.152864847</v>
+        <v>7347555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +743,14 @@
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104154369</v>
+        <v>120288379</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,20 +805,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>St Lappträsk, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862227.2934438487</v>
+        <v>862228</v>
       </c>
       <c r="R3" t="n">
-        <v>7347555.169181026</v>
+        <v>7347558</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,24 +849,14 @@
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,117 +880,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>120288379</v>
-      </c>
-      <c r="B4" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>St Lappträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>862228</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7347558</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Töre</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
